--- a/Personel_Devam_Cizelgesi_Eylul_2026_ERDOGAN_KANAY.xlsx
+++ b/Personel_Devam_Cizelgesi_Eylul_2026_ERDOGAN_KANAY.xlsx
@@ -1614,13 +1614,21 @@
       <c r="B34" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="C34" s="28" t="n"/>
+      <c r="C34" s="28" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="D34" s="6" t="n"/>
       <c r="E34" s="6" t="n"/>
       <c r="F34" s="6" t="n"/>
       <c r="G34" s="6" t="n"/>
       <c r="H34" s="6" t="n"/>
-      <c r="I34" s="28" t="n"/>
+      <c r="I34" s="28" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
       <c r="J34" s="9" t="n"/>
       <c r="K34" s="10" t="n"/>
     </row>
@@ -1628,13 +1636,21 @@
       <c r="B35" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="C35" s="28" t="n"/>
+      <c r="C35" s="28" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="D35" s="6" t="n"/>
       <c r="E35" s="6" t="n"/>
       <c r="F35" s="6" t="n"/>
       <c r="G35" s="6" t="n"/>
       <c r="H35" s="6" t="n"/>
-      <c r="I35" s="28" t="n"/>
+      <c r="I35" s="28" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
       <c r="J35" s="9" t="n"/>
       <c r="K35" s="10" t="n"/>
     </row>
